--- a/cls.var_AMR_ES_FQ_R.xlsx
+++ b/cls.var_AMR_ES_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -32,18 +32,24 @@
     <t xml:space="preserve">log_AMC_EHPAD_macrolides</t>
   </si>
   <si>
+    <t xml:space="preserve">cluster_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">log_AMC_EHPAD_penicillines</t>
   </si>
   <si>
     <t xml:space="preserve">log_AMC_EHPAD_tetracyclines</t>
   </si>
   <si>
-    <t xml:space="preserve">cluster_2</t>
+    <t xml:space="preserve">cluster_3</t>
   </si>
   <si>
     <t xml:space="preserve">log_AMC_EHPAD_tmp_sulfa</t>
   </si>
   <si>
+    <t xml:space="preserve">cluster_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">log_AMC_EHPAD_totale</t>
   </si>
   <si>
@@ -65,6 +71,9 @@
     <t xml:space="preserve">log_AMC_ville_penicillines</t>
   </si>
   <si>
+    <t xml:space="preserve">cluster_5</t>
+  </si>
+  <si>
     <t xml:space="preserve">log_AMC_ville_tetracyclines</t>
   </si>
   <si>
@@ -83,6 +92,9 @@
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
   </si>
   <si>
+    <t xml:space="preserve">prescri_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMR_animaux_compagnie_C3G_R</t>
   </si>
   <si>
@@ -95,9 +107,6 @@
     <t xml:space="preserve">tx_possession_chats</t>
   </si>
   <si>
-    <t xml:space="preserve">cluster_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">tx_possession_chevaux</t>
   </si>
   <si>
@@ -105,9 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">log_UGB_density_SAU_bovine_all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cluster_4</t>
   </si>
   <si>
     <t xml:space="preserve">log_UGB_density_bovine_all</t>
@@ -543,12 +549,12 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -556,23 +562,23 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -580,79 +586,79 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
         <v>19</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -660,31 +666,31 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -692,127 +698,127 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
         <v>3</v>
@@ -820,55 +826,55 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
@@ -876,66 +882,74 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/cls.var_AMR_ES_FQ_R.xlsx
+++ b/cls.var_AMR_ES_FQ_R.xlsx
@@ -741,7 +741,7 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -749,7 +749,7 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -757,7 +757,7 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -765,7 +765,7 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -781,7 +781,7 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -789,7 +789,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -797,7 +797,7 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
